--- a/sample-data/Mau_Import_NhanKhau.xlsx
+++ b/sample-data/Mau_Import_NhanKhau.xlsx
@@ -497,13 +497,13 @@
         <v>Chủ hộ</v>
       </c>
       <c r="K2" s="6" t="str">
-        <v>Nông nghiệp</v>
+        <v>Kinh</v>
       </c>
       <c r="L2" s="6" t="str">
-        <v>Kinh</v>
+        <v>Không</v>
       </c>
       <c r="M2" s="6" t="str">
-        <v>Không</v>
+        <v>Nông nghiệp</v>
       </c>
       <c r="N2" s="6" t="str">
         <v>12/12</v>

--- a/sample-data/Mau_Import_NhanKhau.xlsx
+++ b/sample-data/Mau_Import_NhanKhau.xlsx
@@ -397,6 +397,1608 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="2">
+        <is>
+          <t>HD001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="2">
+        <is>
+          <t>NK001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Văn An</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t>1950-05-12</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t>001050000001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t>Công an tỉnh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t>0912345678</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t>Chu ho</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="2">
+        <is>
+          <t>Kinh</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="2">
+        <is>
+          <t>Nguoi cao tuoi (70+)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr" s="2">
+        <is>
+          <t>Trung hoc</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr" s="2">
+        <is>
+          <t>Da ket hon</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr" s="2">
+        <is>
+          <t>Thuong tru</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr" s="2">
+        <is>
+          <t>O nha</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr" s="2">
+        <is>
+          <t>Con song</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr" s="2">
+        <is>
+          <t>Thôn 9, Xã Minh Châu</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr" s="2">
+        <is>
+          <t>Nguoi cao tuoi</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr" s="2">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr" s="2">
+        <is>
+          <t>Trạm y tế xã Minh Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>HD001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t>NK002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Thị Lan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>1955-07-22</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t>001055000002</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="2">
+        <is>
+          <t>Công an tỉnh</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="2">
+        <is>
+          <t>0912345679</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="2">
+        <is>
+          <t>Vo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr" s="2">
+        <is>
+          <t>Kinh</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr" s="2">
+        <is>
+          <t>Nghi huu</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr" s="2">
+        <is>
+          <t>Trung hoc</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr" s="2">
+        <is>
+          <t>Da ket hon</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr" s="2">
+        <is>
+          <t>Thuong tru</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr" s="2">
+        <is>
+          <t>O nha</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr" s="2">
+        <is>
+          <t>Con song</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr" s="2">
+        <is>
+          <t>Thôn 9, Xã Minh Châu</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr" s="2">
+        <is>
+          <t>HT3012345678901</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr" s="2">
+        <is>
+          <t>Nguoi huong luong huu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr" s="2">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr" s="2">
+        <is>
+          <t>Trạm y tế xã Minh Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t>HD001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t>NK003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Văn Bình</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t>Nam</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t>1988-03-10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t>001088000003</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t>Cục CSQLHC về TTXH</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="2">
+        <is>
+          <t>0912345680</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Văn An</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Thị Lan</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr" s="2">
+        <is>
+          <t>Kinh</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr" s="2">
+        <is>
+          <t>Cong nhan</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr" s="2">
+        <is>
+          <t>THPT</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr" s="2">
+        <is>
+          <t>Da ket hon</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr" s="2">
+        <is>
+          <t>Thuong tru</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr" s="2">
+        <is>
+          <t>O nha</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr" s="2">
+        <is>
+          <t>Con song</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr" s="2">
+        <is>
+          <t>Thôn 9, Xã Minh Châu</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="2">
+        <is>
+          <t>HD001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="2">
+        <is>
+          <t>NK004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="2">
+        <is>
+          <t>Phạm Thị Hoa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t>1990-09-18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="2">
+        <is>
+          <t>001090000004</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="2">
+        <is>
+          <t>2021-02-20</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="2">
+        <is>
+          <t>Cục CSQLHC về TTXH</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="2">
+        <is>
+          <t>0912345681</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr" s="2">
+        <is>
+          <t>Kinh</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr" s="2">
+        <is>
+          <t>Lao dong tu do</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr" s="2">
+        <is>
+          <t>THPT</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr" s="2">
+        <is>
+          <t>Da ket hon</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr" s="2">
+        <is>
+          <t>Thuong tru</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr" s="2">
+        <is>
+          <t>O nha</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr" s="2">
+        <is>
+          <t>Con song</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr" s="2">
+        <is>
+          <t>Thôn 9, Xã Minh Châu</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr" s="2">
+        <is>
+          <t>HG4012345678901</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr" s="2">
+        <is>
+          <t>Ho gia dinh</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr" s="2">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr" s="2">
+        <is>
+          <t>Trạm y tế xã Minh Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t>HD001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="2">
+        <is>
+          <t>NK005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Minh Châu</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t>2013-11-05</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="2">
+        <is>
+          <t>001113000005</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="2">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="2">
+        <is>
+          <t>Công an tỉnh</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr" s="2">
+        <is>
+          <t>Nguyễn Văn Bình</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr" s="2">
+        <is>
+          <t>Phạm Thị Hoa</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr" s="2">
+        <is>
+          <t>Kinh</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr" s="2">
+        <is>
+          <t>Hoc sinh</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr" s="2">
+        <is>
+          <t>Hoc sinh</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr" s="2">
+        <is>
+          <t>Chua ket hon</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr" s="2">
+        <is>
+          <t>Thuong tru</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr" s="2">
+        <is>
+          <t>O nha</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr" s="2">
+        <is>
+          <t>Con song</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr" s="2">
+        <is>
+          <t>Thôn 9, Xã Minh Châu</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr" s="2">
+        <is>
+          <t>Hoc sinh - Sinh vien</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr" s="2">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr" s="2">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr" s="2">
+        <is>
+          <t>Trạm y tế xã Minh Châu</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="2">
+        <is>
+          <t>HD002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t>NK006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="2">
+        <is>
+          <t>Trần Thị Bình</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
+          <t>Nu</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t>1975-02-14</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="2">
+        <is>
+          <t>001075000006</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="2">
+        <is>
+          <t>2019-03-12</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="2">
+        <is>
+          <t>Công an tỉnh</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="2">
+        <is>
+          <t>0987654321</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr" s="2">
+        <is>
+          <t>Chu ho</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr" s="2">
+        <is>
+          <t>Kinh</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr" s="2">
+        <is>
+          <t>Nong nghiep</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr" s="2">
+        <is>
+          <t>THCS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr" s="2">
+        <is>
+          <t>Doc than</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr" s="2">
+        <is>
+          <t>Thuong tru</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr" s="2">
+        <is>
+          <t>O nha</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr" s="2">
+        <is>
+          <t>Con song</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr" s="2">
+        <is>
+          <t>Thôn 9, Xã Minh Châu</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr" s="2">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr" s="2">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr" s="2">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -476,17 +2078,29 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t>Nhap Co, Khong, 1, 0, X. Neu bo trong thi hieu la Khong, rieng BHYT bo trong mac dinh la Co.</t>
+          <t>Nhap Co, Khong, 1, 0, X. Neu bo trong thi hieu la Khong. BHYT chi mac dinh Co theo cot Nghe nghiep khi la Hoc sinh hoac Nguoi cao tuoi (70+).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
         <is>
+          <t>Quan he voi chu ho</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="2">
+        <is>
+          <t>Co the de trong. Sau import he thong chi tu suy luan trong cung ho khi du du lieu bo/me/chu ho va khong ghi de gia tri da nhap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
           <t>Ho co cong/khuyet tat</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="2">
+      <c r="B8" t="inlineStr" s="2">
         <is>
           <t>Khong nhap o mau ho dan. He thong tu suy ra tu cac cot chinh sach cua nhan khau trong ho.</t>
         </is>

--- a/sample-data/Mau_Import_NhanKhau.xlsx
+++ b/sample-data/Mau_Import_NhanKhau.xlsx
@@ -74,6 +74,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2005,6 +2006,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="96" customWidth="1"/>
@@ -2112,6 +2114,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="120" customWidth="1"/>
